--- a/research/traditional_assets/database/data/vietnam/vietnam_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03573</v>
+        <v>0.035</v>
       </c>
       <c r="E2">
-        <v>0.112</v>
+        <v>0.00545</v>
       </c>
       <c r="G2">
-        <v>0.1516061936676681</v>
+        <v>0.1928011404133999</v>
       </c>
       <c r="H2">
-        <v>0.1516061936676681</v>
+        <v>0.1928011404133999</v>
       </c>
       <c r="I2">
-        <v>0.1680147908481627</v>
+        <v>0.1525302922309337</v>
       </c>
       <c r="J2">
-        <v>0.1371472296986159</v>
+        <v>0.1221771463584121</v>
       </c>
       <c r="K2">
-        <v>53.18</v>
+        <v>30.1</v>
       </c>
       <c r="L2">
-        <v>0.1229027039519297</v>
+        <v>0.1072701354240912</v>
       </c>
       <c r="M2">
-        <v>15.32</v>
+        <v>63.8</v>
       </c>
       <c r="N2">
-        <v>0.02144757104857903</v>
+        <v>0.1351122405760271</v>
       </c>
       <c r="O2">
-        <v>0.2880782248965777</v>
+        <v>2.119601328903654</v>
       </c>
       <c r="P2">
-        <v>15.32</v>
+        <v>63.8</v>
       </c>
       <c r="Q2">
-        <v>0.02144757104857903</v>
+        <v>0.1351122405760271</v>
       </c>
       <c r="R2">
-        <v>0.2880782248965777</v>
+        <v>2.119601328903654</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>61.8</v>
+        <v>33.6</v>
       </c>
       <c r="V2">
-        <v>0.08651826963460731</v>
+        <v>0.07115628970775095</v>
       </c>
       <c r="W2">
-        <v>0.1257913451440573</v>
+        <v>0.09772727272727273</v>
       </c>
       <c r="X2">
-        <v>0.06979859114044296</v>
+        <v>0.1086520950779575</v>
       </c>
       <c r="Y2">
-        <v>0.05599275400361439</v>
+        <v>-0.0109248223506848</v>
       </c>
       <c r="Z2">
-        <v>1.299399399399399</v>
+        <v>1.049521244763615</v>
       </c>
       <c r="AA2">
-        <v>0.1678879988354534</v>
+        <v>0.128227510727747</v>
       </c>
       <c r="AB2">
-        <v>0.06953912775428041</v>
+        <v>0.1072720055448425</v>
       </c>
       <c r="AC2">
-        <v>0.09834887108117295</v>
+        <v>0.02095550518290441</v>
       </c>
       <c r="AD2">
-        <v>9.859999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.859999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="AG2">
-        <v>-51.94</v>
+        <v>-17.3</v>
       </c>
       <c r="AH2">
-        <v>0.01361577551922227</v>
+        <v>0.03336745138178096</v>
       </c>
       <c r="AI2">
-        <v>0.0229751141765309</v>
+        <v>0.04804008252284114</v>
       </c>
       <c r="AJ2">
-        <v>-0.0784165710489764</v>
+        <v>-0.03803033633765663</v>
       </c>
       <c r="AK2">
-        <v>-0.1413871951219512</v>
+        <v>-0.05659142950605169</v>
       </c>
       <c r="AL2">
-        <v>0.074</v>
+        <v>0.582</v>
       </c>
       <c r="AM2">
-        <v>-0.125</v>
+        <v>0.582</v>
       </c>
       <c r="AN2">
-        <v>0.1293963254593176</v>
+        <v>0.3468085106382979</v>
       </c>
       <c r="AO2">
-        <v>982.4324324324325</v>
+        <v>73.53951890034364</v>
       </c>
       <c r="AP2">
-        <v>-0.6816272965879264</v>
+        <v>-0.3680851063829788</v>
       </c>
       <c r="AQ2">
-        <v>-581.6</v>
+        <v>73.53951890034364</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00386</v>
+        <v>0.035</v>
       </c>
       <c r="E3">
-        <v>0.113</v>
+        <v>0.00545</v>
       </c>
       <c r="G3">
-        <v>0.2015625</v>
+        <v>0.1928011404133999</v>
       </c>
       <c r="H3">
-        <v>0.2015625</v>
+        <v>0.1928011404133999</v>
       </c>
       <c r="I3">
-        <v>0.225</v>
+        <v>0.1525302922309337</v>
       </c>
       <c r="J3">
-        <v>0.1841651542649728</v>
+        <v>0.1221771463584121</v>
       </c>
       <c r="K3">
-        <v>43.3</v>
+        <v>30.1</v>
       </c>
       <c r="L3">
-        <v>0.169140625</v>
+        <v>0.1072701354240912</v>
       </c>
       <c r="M3">
-        <v>1.32</v>
+        <v>63.8</v>
       </c>
       <c r="N3">
-        <v>0.002619047619047619</v>
+        <v>0.1351122405760271</v>
       </c>
       <c r="O3">
-        <v>0.03048498845265589</v>
+        <v>2.119601328903654</v>
       </c>
       <c r="P3">
-        <v>1.32</v>
+        <v>63.8</v>
       </c>
       <c r="Q3">
-        <v>0.002619047619047619</v>
+        <v>0.1351122405760271</v>
       </c>
       <c r="R3">
-        <v>0.03048498845265589</v>
+        <v>2.119601328903654</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,204 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>50.5</v>
+        <v>33.6</v>
       </c>
       <c r="V3">
-        <v>0.1001984126984127</v>
+        <v>0.07115628970775095</v>
       </c>
       <c r="W3">
-        <v>0.1495165745856353</v>
+        <v>0.09772727272727273</v>
       </c>
       <c r="X3">
-        <v>0.07022330576146005</v>
+        <v>0.1086520950779575</v>
       </c>
       <c r="Y3">
-        <v>0.07929326882417528</v>
+        <v>-0.0109248223506848</v>
       </c>
       <c r="Z3">
-        <v>1.027699718988358</v>
+        <v>1.049521244763615</v>
       </c>
       <c r="AA3">
-        <v>0.1892664772855601</v>
+        <v>0.128227510727747</v>
       </c>
       <c r="AB3">
-        <v>0.06970437898913495</v>
+        <v>0.1072720055448425</v>
       </c>
       <c r="AC3">
-        <v>0.1195620982964252</v>
+        <v>0.02095550518290441</v>
       </c>
       <c r="AD3">
-        <v>9.859999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.859999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="AG3">
-        <v>-40.64</v>
+        <v>-17.3</v>
       </c>
       <c r="AH3">
-        <v>0.01918810570972638</v>
+        <v>0.03336745138178096</v>
       </c>
       <c r="AI3">
-        <v>0.02994593937921399</v>
+        <v>0.04804008252284114</v>
       </c>
       <c r="AJ3">
-        <v>-0.08770718232044199</v>
+        <v>-0.03803033633765663</v>
       </c>
       <c r="AK3">
-        <v>-0.1457884918926675</v>
+        <v>-0.05659142950605169</v>
       </c>
       <c r="AL3">
-        <v>0.074</v>
+        <v>0.582</v>
       </c>
       <c r="AM3">
-        <v>0.074</v>
+        <v>0.582</v>
       </c>
       <c r="AN3">
-        <v>0.1635157545605307</v>
+        <v>0.3468085106382979</v>
       </c>
       <c r="AO3">
-        <v>778.3783783783784</v>
+        <v>73.53951890034364</v>
       </c>
       <c r="AP3">
-        <v>-0.6739635157545606</v>
+        <v>-0.3680851063829788</v>
       </c>
       <c r="AQ3">
-        <v>778.3783783783784</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bao Minh Insurance Corporation (HOSE:BMI)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.06759999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.111</v>
-      </c>
-      <c r="G4">
-        <v>0.07923033389926429</v>
-      </c>
-      <c r="H4">
-        <v>0.07923033389926429</v>
-      </c>
-      <c r="I4">
-        <v>0.08545557441992077</v>
-      </c>
-      <c r="J4">
-        <v>0.06956507504431567</v>
-      </c>
-      <c r="K4">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="L4">
-        <v>0.05591397849462366</v>
-      </c>
-      <c r="M4">
-        <v>14</v>
-      </c>
-      <c r="N4">
-        <v>0.06657156443176414</v>
-      </c>
-      <c r="O4">
-        <v>1.417004048582996</v>
-      </c>
-      <c r="P4">
-        <v>14</v>
-      </c>
-      <c r="Q4">
-        <v>0.06657156443176414</v>
-      </c>
-      <c r="R4">
-        <v>1.417004048582996</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>11.3</v>
-      </c>
-      <c r="V4">
-        <v>0.05373276271992392</v>
-      </c>
-      <c r="W4">
-        <v>0.1020661157024794</v>
-      </c>
-      <c r="X4">
-        <v>0.06937387651942586</v>
-      </c>
-      <c r="Y4">
-        <v>0.03269223918305349</v>
-      </c>
-      <c r="Z4">
-        <v>2.106078665077473</v>
-      </c>
-      <c r="AA4">
-        <v>0.1465095203853466</v>
-      </c>
-      <c r="AB4">
-        <v>0.06937387651942586</v>
-      </c>
-      <c r="AC4">
-        <v>0.07713564386592073</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-11.3</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.05678391959798995</v>
-      </c>
-      <c r="AK4">
-        <v>-0.1275395033860045</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-0.199</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>-0.7106918238993711</v>
-      </c>
-      <c r="AQ4">
-        <v>-75.87939698492461</v>
+        <v>73.53951890034364</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.035</v>
+        <v>0.0538</v>
       </c>
       <c r="E2">
-        <v>0.00545</v>
+        <v>0.129</v>
       </c>
       <c r="G2">
-        <v>0.1928011404133999</v>
+        <v>0.1646987587042083</v>
       </c>
       <c r="H2">
-        <v>0.1928011404133999</v>
+        <v>0.1646987587042083</v>
       </c>
       <c r="I2">
-        <v>0.1525302922309337</v>
+        <v>0.1889191643960036</v>
       </c>
       <c r="J2">
-        <v>0.1221771463584121</v>
+        <v>0.1544361496307851</v>
       </c>
       <c r="K2">
-        <v>30.1</v>
+        <v>42</v>
       </c>
       <c r="L2">
-        <v>0.1072701354240912</v>
+        <v>0.1271571298819255</v>
       </c>
       <c r="M2">
-        <v>63.8</v>
+        <v>1.22</v>
       </c>
       <c r="N2">
-        <v>0.1351122405760271</v>
+        <v>0.002835231234022775</v>
       </c>
       <c r="O2">
-        <v>2.119601328903654</v>
+        <v>0.02904761904761905</v>
       </c>
       <c r="P2">
-        <v>63.8</v>
+        <v>1.22</v>
       </c>
       <c r="Q2">
-        <v>0.1351122405760271</v>
+        <v>0.002835231234022775</v>
       </c>
       <c r="R2">
-        <v>2.119601328903654</v>
+        <v>0.02904761904761905</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>33.6</v>
+        <v>41.2</v>
       </c>
       <c r="V2">
-        <v>0.07115628970775095</v>
-      </c>
-      <c r="W2">
-        <v>0.09772727272727273</v>
+        <v>0.09574715314896584</v>
       </c>
       <c r="X2">
-        <v>0.1086520950779575</v>
-      </c>
-      <c r="Y2">
-        <v>-0.0109248223506848</v>
-      </c>
-      <c r="Z2">
-        <v>1.049521244763615</v>
-      </c>
-      <c r="AA2">
-        <v>0.128227510727747</v>
+        <v>0.0979502601262677</v>
       </c>
       <c r="AB2">
-        <v>0.1072720055448425</v>
-      </c>
-      <c r="AC2">
-        <v>0.02095550518290441</v>
+        <v>0.09562401782303327</v>
       </c>
       <c r="AD2">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>-17.3</v>
+        <v>-11.2</v>
       </c>
       <c r="AH2">
-        <v>0.03336745138178096</v>
+        <v>0.0651748859439496</v>
       </c>
       <c r="AI2">
-        <v>0.04804008252284114</v>
+        <v>0.08342602892102335</v>
       </c>
       <c r="AJ2">
-        <v>-0.03803033633765663</v>
+        <v>-0.02672393223574326</v>
       </c>
       <c r="AK2">
-        <v>-0.05659142950605169</v>
+        <v>-0.03517587939698493</v>
       </c>
       <c r="AL2">
-        <v>0.582</v>
+        <v>1.25</v>
       </c>
       <c r="AM2">
-        <v>0.582</v>
+        <v>1.25</v>
       </c>
       <c r="AN2">
-        <v>0.3468085106382979</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AO2">
-        <v>73.53951890034364</v>
+        <v>49.92</v>
       </c>
       <c r="AP2">
-        <v>-0.3680851063829788</v>
+        <v>-0.1723076923076924</v>
       </c>
       <c r="AQ2">
-        <v>73.53951890034364</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +707,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.035</v>
+        <v>0.0538</v>
       </c>
       <c r="E3">
-        <v>0.00545</v>
+        <v>0.129</v>
       </c>
       <c r="G3">
-        <v>0.1928011404133999</v>
+        <v>0.1646987587042083</v>
       </c>
       <c r="H3">
-        <v>0.1928011404133999</v>
+        <v>0.1646987587042083</v>
       </c>
       <c r="I3">
-        <v>0.1525302922309337</v>
+        <v>0.1889191643960036</v>
       </c>
       <c r="J3">
-        <v>0.1221771463584121</v>
+        <v>0.1544361496307851</v>
       </c>
       <c r="K3">
-        <v>30.1</v>
+        <v>42</v>
       </c>
       <c r="L3">
-        <v>0.1072701354240912</v>
+        <v>0.1271571298819255</v>
       </c>
       <c r="M3">
-        <v>63.8</v>
+        <v>1.22</v>
       </c>
       <c r="N3">
-        <v>0.1351122405760271</v>
+        <v>0.002835231234022775</v>
       </c>
       <c r="O3">
-        <v>2.119601328903654</v>
+        <v>0.02904761904761905</v>
       </c>
       <c r="P3">
-        <v>63.8</v>
+        <v>1.22</v>
       </c>
       <c r="Q3">
-        <v>0.1351122405760271</v>
+        <v>0.002835231234022775</v>
       </c>
       <c r="R3">
-        <v>2.119601328903654</v>
+        <v>0.02904761904761905</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +755,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>33.6</v>
+        <v>41.2</v>
       </c>
       <c r="V3">
-        <v>0.07115628970775095</v>
-      </c>
-      <c r="W3">
-        <v>0.09772727272727273</v>
+        <v>0.09574715314896584</v>
       </c>
       <c r="X3">
-        <v>0.1086520950779575</v>
-      </c>
-      <c r="Y3">
-        <v>-0.0109248223506848</v>
-      </c>
-      <c r="Z3">
-        <v>1.049521244763615</v>
-      </c>
-      <c r="AA3">
-        <v>0.128227510727747</v>
+        <v>0.0979502601262677</v>
       </c>
       <c r="AB3">
-        <v>0.1072720055448425</v>
-      </c>
-      <c r="AC3">
-        <v>0.02095550518290441</v>
+        <v>0.09562401782303327</v>
       </c>
       <c r="AD3">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="AG3">
-        <v>-17.3</v>
+        <v>-11.2</v>
       </c>
       <c r="AH3">
-        <v>0.03336745138178096</v>
+        <v>0.0651748859439496</v>
       </c>
       <c r="AI3">
-        <v>0.04804008252284114</v>
+        <v>0.08342602892102335</v>
       </c>
       <c r="AJ3">
-        <v>-0.03803033633765663</v>
+        <v>-0.02672393223574326</v>
       </c>
       <c r="AK3">
-        <v>-0.05659142950605169</v>
+        <v>-0.03517587939698493</v>
       </c>
       <c r="AL3">
-        <v>0.582</v>
+        <v>1.25</v>
       </c>
       <c r="AM3">
-        <v>0.582</v>
+        <v>1.25</v>
       </c>
       <c r="AN3">
-        <v>0.3468085106382979</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AO3">
-        <v>73.53951890034364</v>
+        <v>49.92</v>
       </c>
       <c r="AP3">
-        <v>-0.3680851063829788</v>
+        <v>-0.1723076923076924</v>
       </c>
       <c r="AQ3">
-        <v>73.53951890034364</v>
+        <v>49.92</v>
       </c>
     </row>
   </sheetData>
